--- a/Exp3_PTO_GRPO/eda/results/all/tables/3_mechanism/3_mechanism.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/all/tables/3_mechanism/3_mechanism.xlsx
@@ -429,27 +429,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>B3_Q</t>
+          <t>B3_Q_per_turn</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>B4_SR</t>
+          <t>B4_SR_per_turn</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>B5_CR</t>
+          <t>B5_CR_per_turn</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>B6_AF</t>
+          <t>B6_AF_per_turn</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>B2_Persuade</t>
+          <t>B2_Persuade_per_turn</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -483,19 +483,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>6.385</v>
+        <v>0.446</v>
       </c>
       <c r="D2" t="n">
-        <v>2.698</v>
+        <v>0.179</v>
       </c>
       <c r="E2" t="n">
-        <v>1.365</v>
+        <v>0.093</v>
       </c>
       <c r="F2" t="n">
-        <v>0.521</v>
+        <v>0.029</v>
       </c>
       <c r="G2" t="n">
-        <v>1.167</v>
+        <v>0.089</v>
       </c>
       <c r="H2" t="n">
         <v>0.7</v>
@@ -520,19 +520,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>5.573</v>
+        <v>0.458</v>
       </c>
       <c r="D3" t="n">
-        <v>2.271</v>
+        <v>0.165</v>
       </c>
       <c r="E3" t="n">
-        <v>1.062</v>
+        <v>0.075</v>
       </c>
       <c r="F3" t="n">
-        <v>0.385</v>
+        <v>0.023</v>
       </c>
       <c r="G3" t="n">
-        <v>1.302</v>
+        <v>0.104</v>
       </c>
       <c r="H3" t="n">
         <v>0.632</v>
@@ -557,19 +557,19 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>6.594</v>
+        <v>0.423</v>
       </c>
       <c r="D4" t="n">
-        <v>3.104</v>
+        <v>0.189</v>
       </c>
       <c r="E4" t="n">
-        <v>1.635</v>
+        <v>0.102</v>
       </c>
       <c r="F4" t="n">
-        <v>0.594</v>
+        <v>0.032</v>
       </c>
       <c r="G4" t="n">
-        <v>1.427</v>
+        <v>0.098</v>
       </c>
       <c r="H4" t="n">
         <v>0.741</v>
@@ -594,19 +594,19 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>5.396</v>
+        <v>0.402</v>
       </c>
       <c r="D5" t="n">
-        <v>2.427</v>
+        <v>0.163</v>
       </c>
       <c r="E5" t="n">
-        <v>1.365</v>
+        <v>0.092</v>
       </c>
       <c r="F5" t="n">
-        <v>0.479</v>
+        <v>0.03</v>
       </c>
       <c r="G5" t="n">
-        <v>1.802</v>
+        <v>0.137</v>
       </c>
       <c r="H5" t="n">
         <v>0.673</v>
@@ -631,19 +631,19 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>5.542</v>
+        <v>0.374</v>
       </c>
       <c r="D6" t="n">
-        <v>2.677</v>
+        <v>0.164</v>
       </c>
       <c r="E6" t="n">
-        <v>1.531</v>
+        <v>0.097</v>
       </c>
       <c r="F6" t="n">
-        <v>0.906</v>
+        <v>0.054</v>
       </c>
       <c r="G6" t="n">
-        <v>2.146</v>
+        <v>0.148</v>
       </c>
       <c r="H6" t="n">
         <v>0.732</v>
@@ -668,19 +668,19 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>5.396</v>
+        <v>0.361</v>
       </c>
       <c r="D7" t="n">
-        <v>2.792</v>
+        <v>0.174</v>
       </c>
       <c r="E7" t="n">
-        <v>1.448</v>
+        <v>0.09</v>
       </c>
       <c r="F7" t="n">
-        <v>0.865</v>
+        <v>0.055</v>
       </c>
       <c r="G7" t="n">
-        <v>2.125</v>
+        <v>0.148</v>
       </c>
       <c r="H7" t="n">
         <v>0.776</v>
@@ -705,19 +705,19 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>5.635</v>
+        <v>0.353</v>
       </c>
       <c r="D8" t="n">
-        <v>3.104</v>
+        <v>0.183</v>
       </c>
       <c r="E8" t="n">
-        <v>1.802</v>
+        <v>0.117</v>
       </c>
       <c r="F8" t="n">
-        <v>0.844</v>
+        <v>0.052</v>
       </c>
       <c r="G8" t="n">
-        <v>2.104</v>
+        <v>0.139</v>
       </c>
       <c r="H8" t="n">
         <v>0.905</v>
@@ -742,19 +742,19 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>4.99</v>
+        <v>0.354</v>
       </c>
       <c r="D9" t="n">
-        <v>2.75</v>
+        <v>0.182</v>
       </c>
       <c r="E9" t="n">
-        <v>1.458</v>
+        <v>0.096</v>
       </c>
       <c r="F9" t="n">
-        <v>1.177</v>
+        <v>0.081</v>
       </c>
       <c r="G9" t="n">
-        <v>2.073</v>
+        <v>0.152</v>
       </c>
       <c r="H9" t="n">
         <v>0.854</v>
@@ -779,19 +779,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>4.104</v>
+        <v>0.343</v>
       </c>
       <c r="D10" t="n">
-        <v>2.396</v>
+        <v>0.19</v>
       </c>
       <c r="E10" t="n">
-        <v>1.552</v>
+        <v>0.131</v>
       </c>
       <c r="F10" t="n">
-        <v>1.208</v>
+        <v>0.095</v>
       </c>
       <c r="G10" t="n">
-        <v>1.729</v>
+        <v>0.151</v>
       </c>
       <c r="H10" t="n">
         <v>1.043</v>
@@ -816,19 +816,19 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>6.438</v>
+        <v>0.347</v>
       </c>
       <c r="D11" t="n">
-        <v>3.958</v>
+        <v>0.2</v>
       </c>
       <c r="E11" t="n">
-        <v>2.083</v>
+        <v>0.112</v>
       </c>
       <c r="F11" t="n">
-        <v>1.583</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>2.188</v>
+        <v>0.122</v>
       </c>
       <c r="H11" t="n">
         <v>0.905</v>
@@ -853,19 +853,19 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>4.115</v>
+        <v>0.319</v>
       </c>
       <c r="D12" t="n">
-        <v>2.74</v>
+        <v>0.212</v>
       </c>
       <c r="E12" t="n">
-        <v>2.021</v>
+        <v>0.167</v>
       </c>
       <c r="F12" t="n">
-        <v>1.979</v>
+        <v>0.154</v>
       </c>
       <c r="G12" t="n">
-        <v>1.375</v>
+        <v>0.109</v>
       </c>
       <c r="H12" t="n">
         <v>1.435</v>
@@ -890,19 +890,19 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>6.552</v>
+        <v>0.471</v>
       </c>
       <c r="D13" t="n">
-        <v>2.896</v>
+        <v>0.199</v>
       </c>
       <c r="E13" t="n">
-        <v>1.292</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.417</v>
+        <v>0.026</v>
       </c>
       <c r="G13" t="n">
-        <v>1.042</v>
+        <v>0.078</v>
       </c>
       <c r="H13" t="n">
         <v>0.765</v>
@@ -927,19 +927,19 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>6.125</v>
+        <v>0.461</v>
       </c>
       <c r="D14" t="n">
-        <v>2.49</v>
+        <v>0.152</v>
       </c>
       <c r="E14" t="n">
-        <v>1.26</v>
+        <v>0.073</v>
       </c>
       <c r="F14" t="n">
-        <v>0.438</v>
+        <v>0.023</v>
       </c>
       <c r="G14" t="n">
-        <v>1.333</v>
+        <v>0.101</v>
       </c>
       <c r="H14" t="n">
         <v>0.656</v>
@@ -964,19 +964,19 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>6.448</v>
+        <v>0.485</v>
       </c>
       <c r="D15" t="n">
-        <v>2.656</v>
+        <v>0.175</v>
       </c>
       <c r="E15" t="n">
-        <v>1.302</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.417</v>
+        <v>0.025</v>
       </c>
       <c r="G15" t="n">
-        <v>1.281</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>0.61</v>
@@ -1001,19 +1001,19 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>5.802</v>
+        <v>0.48</v>
       </c>
       <c r="D16" t="n">
-        <v>2.562</v>
+        <v>0.179</v>
       </c>
       <c r="E16" t="n">
-        <v>1.271</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.427</v>
+        <v>0.025</v>
       </c>
       <c r="G16" t="n">
-        <v>1.094</v>
+        <v>0.09</v>
       </c>
       <c r="H16" t="n">
         <v>0.612</v>
@@ -1038,19 +1038,19 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>5.854</v>
+        <v>0.451</v>
       </c>
       <c r="D17" t="n">
-        <v>2.677</v>
+        <v>0.178</v>
       </c>
       <c r="E17" t="n">
-        <v>1.271</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.479</v>
+        <v>0.03</v>
       </c>
       <c r="G17" t="n">
-        <v>1.552</v>
+        <v>0.112</v>
       </c>
       <c r="H17" t="n">
         <v>0.764</v>
@@ -1075,19 +1075,19 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>4.958</v>
+        <v>0.48</v>
       </c>
       <c r="D18" t="n">
-        <v>2.281</v>
+        <v>0.171</v>
       </c>
       <c r="E18" t="n">
-        <v>1.229</v>
+        <v>0.089</v>
       </c>
       <c r="F18" t="n">
-        <v>0.427</v>
+        <v>0.031</v>
       </c>
       <c r="G18" t="n">
-        <v>1.573</v>
+        <v>0.128</v>
       </c>
       <c r="H18" t="n">
         <v>0.673</v>
@@ -1112,19 +1112,19 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>4.635</v>
+        <v>0.451</v>
       </c>
       <c r="D19" t="n">
-        <v>2.104</v>
+        <v>0.152</v>
       </c>
       <c r="E19" t="n">
-        <v>1.198</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.646</v>
+        <v>0.041</v>
       </c>
       <c r="G19" t="n">
-        <v>1.708</v>
+        <v>0.136</v>
       </c>
       <c r="H19" t="n">
         <v>0.65</v>
@@ -1149,19 +1149,19 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>4.615</v>
+        <v>0.446</v>
       </c>
       <c r="D20" t="n">
-        <v>1.958</v>
+        <v>0.153</v>
       </c>
       <c r="E20" t="n">
-        <v>1.073</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.521</v>
+        <v>0.037</v>
       </c>
       <c r="G20" t="n">
-        <v>1.781</v>
+        <v>0.148</v>
       </c>
       <c r="H20" t="n">
         <v>0.607</v>
@@ -1186,19 +1186,19 @@
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>4.417</v>
+        <v>0.498</v>
       </c>
       <c r="D21" t="n">
-        <v>1.896</v>
+        <v>0.159</v>
       </c>
       <c r="E21" t="n">
-        <v>1.073</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.844</v>
+        <v>0.065</v>
       </c>
       <c r="G21" t="n">
-        <v>1.677</v>
+        <v>0.149</v>
       </c>
       <c r="H21" t="n">
         <v>0.652</v>
@@ -1223,19 +1223,19 @@
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>4.458</v>
+        <v>0.442</v>
       </c>
       <c r="D22" t="n">
-        <v>1.865</v>
+        <v>0.141</v>
       </c>
       <c r="E22" t="n">
-        <v>1.052</v>
+        <v>0.08</v>
       </c>
       <c r="F22" t="n">
-        <v>1.115</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>1.708</v>
+        <v>0.144</v>
       </c>
       <c r="H22" t="n">
         <v>0.606</v>
@@ -1260,19 +1260,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>3.938</v>
+        <v>0.406</v>
       </c>
       <c r="D23" t="n">
-        <v>1.885</v>
+        <v>0.174</v>
       </c>
       <c r="E23" t="n">
-        <v>1.156</v>
+        <v>0.106</v>
       </c>
       <c r="F23" t="n">
-        <v>1.073</v>
+        <v>0.091</v>
       </c>
       <c r="G23" t="n">
-        <v>1.583</v>
+        <v>0.149</v>
       </c>
       <c r="H23" t="n">
         <v>0.798</v>
@@ -1297,19 +1297,19 @@
         <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>3.594</v>
+        <v>0.394</v>
       </c>
       <c r="D24" t="n">
-        <v>1.646</v>
+        <v>0.153</v>
       </c>
       <c r="E24" t="n">
-        <v>1.052</v>
+        <v>0.097</v>
       </c>
       <c r="F24" t="n">
-        <v>1.365</v>
+        <v>0.131</v>
       </c>
       <c r="G24" t="n">
-        <v>1.562</v>
+        <v>0.163</v>
       </c>
       <c r="H24" t="n">
         <v>0.727</v>
@@ -1334,19 +1334,19 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>3.844</v>
+        <v>0.405</v>
       </c>
       <c r="D25" t="n">
-        <v>1.698</v>
+        <v>0.153</v>
       </c>
       <c r="E25" t="n">
-        <v>1.125</v>
+        <v>0.105</v>
       </c>
       <c r="F25" t="n">
-        <v>1.635</v>
+        <v>0.142</v>
       </c>
       <c r="G25" t="n">
-        <v>1.562</v>
+        <v>0.15</v>
       </c>
       <c r="H25" t="n">
         <v>0.75</v>
@@ -1371,19 +1371,19 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>7.229</v>
+        <v>0.476</v>
       </c>
       <c r="D26" t="n">
-        <v>2.719</v>
+        <v>0.175</v>
       </c>
       <c r="E26" t="n">
-        <v>1.312</v>
+        <v>0.078</v>
       </c>
       <c r="F26" t="n">
-        <v>0.542</v>
+        <v>0.029</v>
       </c>
       <c r="G26" t="n">
-        <v>1.281</v>
+        <v>0.091</v>
       </c>
       <c r="H26" t="n">
         <v>0.728</v>
@@ -1408,19 +1408,19 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>6.01</v>
+        <v>0.486</v>
       </c>
       <c r="D27" t="n">
-        <v>2.635</v>
+        <v>0.179</v>
       </c>
       <c r="E27" t="n">
-        <v>1.26</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.354</v>
+        <v>0.023</v>
       </c>
       <c r="G27" t="n">
-        <v>1.094</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>0.626</v>
@@ -1445,19 +1445,19 @@
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>5.271</v>
+        <v>0.423</v>
       </c>
       <c r="D28" t="n">
-        <v>2.615</v>
+        <v>0.184</v>
       </c>
       <c r="E28" t="n">
-        <v>1.427</v>
+        <v>0.097</v>
       </c>
       <c r="F28" t="n">
-        <v>0.49</v>
+        <v>0.031</v>
       </c>
       <c r="G28" t="n">
-        <v>1.635</v>
+        <v>0.118</v>
       </c>
       <c r="H28" t="n">
         <v>0.764</v>
@@ -1482,19 +1482,19 @@
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>5.062</v>
+        <v>0.454</v>
       </c>
       <c r="D29" t="n">
-        <v>2.396</v>
+        <v>0.161</v>
       </c>
       <c r="E29" t="n">
-        <v>1.396</v>
+        <v>0.092</v>
       </c>
       <c r="F29" t="n">
-        <v>0.479</v>
+        <v>0.026</v>
       </c>
       <c r="G29" t="n">
-        <v>1.615</v>
+        <v>0.123</v>
       </c>
       <c r="H29" t="n">
         <v>0.6820000000000001</v>
@@ -1519,19 +1519,19 @@
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>4.49</v>
+        <v>0.444</v>
       </c>
       <c r="D30" t="n">
-        <v>1.875</v>
+        <v>0.137</v>
       </c>
       <c r="E30" t="n">
-        <v>1.021</v>
+        <v>0.078</v>
       </c>
       <c r="F30" t="n">
-        <v>0.51</v>
+        <v>0.032</v>
       </c>
       <c r="G30" t="n">
-        <v>1.677</v>
+        <v>0.144</v>
       </c>
       <c r="H30" t="n">
         <v>0.589</v>

--- a/Exp3_PTO_GRPO/eda/results/all/tables/3_mechanism/3_mechanism.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/all/tables/3_mechanism/3_mechanism.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="behavior_by_iter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="miti_threshold_verdicts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mici_behavior_by_iter" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pct_patient_by_iter" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="q2_item_deltas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,20 +458,30 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>B1_GI_per_turn</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>B7_Seek_per_turn</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>RtoQ</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Empathy</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>loop</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>q_per_turn</t>
         </is>
@@ -498,15 +512,21 @@
         <v>0.089</v>
       </c>
       <c r="H2" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.7</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>3.469</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.479</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.829</v>
       </c>
     </row>
@@ -535,15 +555,21 @@
         <v>0.104</v>
       </c>
       <c r="H3" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.632</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>3.521</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.365</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.6820000000000001</v>
       </c>
     </row>
@@ -572,15 +598,21 @@
         <v>0.098</v>
       </c>
       <c r="H4" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.741</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>3.792</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.354</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -609,15 +641,21 @@
         <v>0.137</v>
       </c>
       <c r="H5" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.673</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>4.167</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.727</v>
       </c>
     </row>
@@ -646,15 +684,21 @@
         <v>0.148</v>
       </c>
       <c r="H6" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.732</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>4.302</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.042</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.496</v>
       </c>
     </row>
@@ -683,15 +727,21 @@
         <v>0.148</v>
       </c>
       <c r="H7" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.776</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>4.219</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.021</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.324</v>
       </c>
     </row>
@@ -720,15 +770,21 @@
         <v>0.139</v>
       </c>
       <c r="H8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.905</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>4.25</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.073</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.269</v>
       </c>
     </row>
@@ -757,15 +813,21 @@
         <v>0.152</v>
       </c>
       <c r="H9" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.854</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>4.396</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.01</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.228</v>
       </c>
     </row>
@@ -794,15 +856,21 @@
         <v>0.151</v>
       </c>
       <c r="H10" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="J10" t="n">
         <v>1.043</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>4.552</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.01</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.231</v>
       </c>
     </row>
@@ -831,15 +899,21 @@
         <v>0.122</v>
       </c>
       <c r="H11" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.905</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>4.292</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.125</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.158</v>
       </c>
     </row>
@@ -868,15 +942,21 @@
         <v>0.109</v>
       </c>
       <c r="H12" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="J12" t="n">
         <v>1.435</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>4.26</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.151</v>
       </c>
     </row>
@@ -905,15 +985,21 @@
         <v>0.078</v>
       </c>
       <c r="H13" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="J13" t="n">
         <v>0.765</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>3.458</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.49</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>0.74</v>
       </c>
     </row>
@@ -942,15 +1028,21 @@
         <v>0.101</v>
       </c>
       <c r="H14" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="J14" t="n">
         <v>0.656</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>3.646</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.354</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.884</v>
       </c>
     </row>
@@ -979,15 +1071,21 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="H15" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.61</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>3.448</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.49</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -1016,15 +1114,21 @@
         <v>0.09</v>
       </c>
       <c r="H16" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.612</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>3.698</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.375</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.844</v>
       </c>
     </row>
@@ -1053,15 +1157,21 @@
         <v>0.112</v>
       </c>
       <c r="H17" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.764</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>3.833</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.271</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.779</v>
       </c>
     </row>
@@ -1090,15 +1200,21 @@
         <v>0.128</v>
       </c>
       <c r="H18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.673</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>4.01</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.104</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.856</v>
       </c>
     </row>
@@ -1127,15 +1243,21 @@
         <v>0.136</v>
       </c>
       <c r="H19" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.65</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>4.198</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.042</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.752</v>
       </c>
     </row>
@@ -1164,15 +1286,21 @@
         <v>0.148</v>
       </c>
       <c r="H20" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="J20" t="n">
         <v>0.607</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>4.26</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.01</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.804</v>
       </c>
     </row>
@@ -1201,15 +1329,21 @@
         <v>0.149</v>
       </c>
       <c r="H21" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="J21" t="n">
         <v>0.652</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>4.427</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.01</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.742</v>
       </c>
     </row>
@@ -1238,15 +1372,21 @@
         <v>0.144</v>
       </c>
       <c r="H22" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="J22" t="n">
         <v>0.606</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>4.396</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.01</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.68</v>
       </c>
     </row>
@@ -1275,15 +1415,21 @@
         <v>0.149</v>
       </c>
       <c r="H23" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="J23" t="n">
         <v>0.798</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>4.531</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.01</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.675</v>
       </c>
     </row>
@@ -1312,15 +1458,21 @@
         <v>0.163</v>
       </c>
       <c r="H24" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J24" t="n">
         <v>0.727</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>4.573</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.647</v>
       </c>
     </row>
@@ -1349,15 +1501,21 @@
         <v>0.15</v>
       </c>
       <c r="H25" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="J25" t="n">
         <v>0.75</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>4.615</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -1386,15 +1544,21 @@
         <v>0.091</v>
       </c>
       <c r="H26" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="J26" t="n">
         <v>0.728</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>3.448</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.448</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.766</v>
       </c>
     </row>
@@ -1423,15 +1587,21 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="H27" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J27" t="n">
         <v>0.626</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>3.51</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.427</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.767</v>
       </c>
     </row>
@@ -1460,15 +1630,21 @@
         <v>0.118</v>
       </c>
       <c r="H28" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J28" t="n">
         <v>0.764</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>3.74</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.417</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.779</v>
       </c>
     </row>
@@ -1497,15 +1673,21 @@
         <v>0.123</v>
       </c>
       <c r="H29" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="J29" t="n">
         <v>0.6820000000000001</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>3.938</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.219</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.823</v>
       </c>
     </row>
@@ -1534,16 +1716,4660 @@
         <v>0.144</v>
       </c>
       <c r="H30" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="J30" t="n">
         <v>0.589</v>
       </c>
+      <c r="K30" t="n">
+        <v>4.146</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.766</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Reflection:Question (MITI)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>% Complex Reflections (MITI)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Technical global (MITI)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Relational global (MITI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GRPO (K=0)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>base (iter 0)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.70 ✗</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.30 ✗</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3.05 ✓fair</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3.40 ✗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GRPO (K=0)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>final (iter 10)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.43 ✓fair</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.41 ✓fair</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.64 ✓fair</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4.20 ✓good</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GRPO (K=5)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>base (iter 0)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.77 ✗</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.28 ✗</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2.94 ✗</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3.30 ✗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GRPO (K=5)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>final (iter 1)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.66 ✗</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.30 ✗</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.05 ✓fair</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3.55 ✓fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PTO (K=0)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>base (iter 0)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.61 ✗</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.31 ✗</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2.92 ✗</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3.34 ✗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PTO (K=0)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>final (iter 10)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.75 ✗</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.36 ✗</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.93 ✓fair</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4.61 ✓good</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PTO (K=5)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>base (iter 0)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.73 ✗</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.29 ✗</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2.95 ✗</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3.34 ✗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PTO (K=5)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>final (iter 4)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.59 ✗</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.32 ✗</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.53 ✓fair</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4.08 ✓good</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>iteration</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MICI_Severity</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>MICI_Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>MICI_Confront_rate</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>MICI_AdviseNoPermission_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MICI_Warn_rate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>MICI_Direct_rate</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>MICI_Judge_rate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MICI_OverPraise_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.542</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.698</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.854</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.031</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.698</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.427</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.458</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.029</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.017</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.406</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.034</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.037</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.077</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.299</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.188</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.017</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.938</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2.854</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.063</v>
+      </c>
       <c r="I30" t="n">
-        <v>4.146</v>
+        <v>0.003</v>
       </c>
       <c r="J30" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.766</v>
+        <v>0.043</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>iteration</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>PCT_Importance</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PCT_Confidence</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PCT_Readiness</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>PCT_GlobalMean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PCT_ChangeProp</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>PCT_ChangeTalk_prop</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PCT_SustainTalk_prop</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>PCT_Neutral_prop</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.101</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.115</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.458</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.823</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.292</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.191</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.149</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.141</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.948</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.309</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.159</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.427</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.938</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.253</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.146</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.427</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.906</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.458</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.264</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.927</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.316</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.562</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.052</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.729</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.448</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.115</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.708</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.944</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.208</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.719</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.042</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.708</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.323</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.729</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.062</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.038</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.159</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.469</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.844</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.174</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.132</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.427</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.719</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.083</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.076</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.458</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.854</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.229</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.181</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.479</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.906</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.264</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.594</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.131</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.542</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.969</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.688</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.052</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.469</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.562</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.969</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.531</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.354</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.688</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.688</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.483</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.156</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.583</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.802</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.604</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.113</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.354</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.708</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.069</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.031</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.076</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.147</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.448</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.174</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.145</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.646</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.969</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.479</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3.719</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.635</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.458</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.127</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>final_iter</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>revealed his thinking</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.708</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.073</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>put himself in my shoes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.802</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>took charge</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Direction/control</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.729</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.719</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>shared his feelings</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.219</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.083</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.865</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>treated me as equal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.229</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.833</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>did not judge me</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.823</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>knew how I was feeling</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.281</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.094</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>said when happy/sad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.802</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>a 'warm' partner</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.031</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.823</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.792</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>understood me</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.979</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>relaxed and secure</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.531</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.719</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>comfortable talking</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.542</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.698</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>17</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>made me feel close</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.198</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.677</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>expressed himself</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.542</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>16</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>made me feel cared for</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.281</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.938</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.656</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>no difficulty w/ words</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.562</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.646</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sense of who he was</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.094</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.656</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>made me feel close</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.052</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.448</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>no difficulty w/ words</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.417</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.438</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>comfortable talking</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.417</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.427</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>expressed himself</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.427</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>treated me as equal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.688</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.427</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>14</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>did not judge me</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.385</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.802</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.417</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>16</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>made me feel cared for</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.552</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.417</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>relaxed and secure</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.802</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.396</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>put himself in my shoes</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.688</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.385</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>knew how I was feeling</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.156</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>13</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>a 'warm' partner</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.302</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.323</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>took charge</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Direction/control</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.677</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.312</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>understood me</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.458</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.281</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>said when happy/sad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>revealed his thinking</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.854</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sense of who he was</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.042</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.271</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.229</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>shared his feelings</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.229</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>put himself in my shoes</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.781</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.542</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>16</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>made me feel cared for</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.698</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.531</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>revealed his thinking</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.115</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.479</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>9</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>took charge</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Direction/control</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.729</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.479</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>17</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>made me feel close</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.052</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4.521</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.469</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>15</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>treated me as equal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4.781</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.438</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>14</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>did not judge me</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>10</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.427</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>13</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>a 'warm' partner</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.312</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>said when happy/sad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3.552</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>relaxed and secure</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>10</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3.479</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>12</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>expressed himself</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>10</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>shared his feelings</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.156</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3.385</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.229</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>comfortable talking</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.521</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.729</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.208</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>11</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>no difficulty w/ words</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.531</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.208</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>understood me</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.292</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4.427</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.135</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>knew how I was feeling</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4.427</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.094</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sense of who he was</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3.927</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.854</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>14</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>did not judge me</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4.562</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.167</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>16</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>made me feel cared for</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.188</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4.292</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.104</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>17</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>made me feel close</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4.219</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.094</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>treated me as equal</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Non-judgment/equality</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.354</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4.427</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.073</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>9</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>took charge</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Direction/control</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.708</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.958</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>13</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>a 'warm' partner</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Warmth/closeness</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.052</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3.958</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.906</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>put himself in my shoes</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.719</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.896</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>understood me</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="G60" t="n">
+        <v>4.021</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>8</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>relaxed and secure</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.469</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.865</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>12</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>expressed himself</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="G62" t="n">
+        <v>4.354</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.865</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>comfortable talking</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4.344</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.844</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>11</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>no difficulty w/ words</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Fluency/ease</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3.531</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4.365</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.833</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>knew how I was feeling</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Empathy/understanding</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3.271</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4.073</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.802</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>revealed his thinking</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>10</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>said when happy/sad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3.031</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.771</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sense of who he was</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3.646</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>shared his feelings</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Self-disclosure</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2.688</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.552</v>
       </c>
     </row>
   </sheetData>
